--- a/hardware_analysis.xlsx
+++ b/hardware_analysis.xlsx
@@ -29,7 +29,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
       <sz val="14"/>
     </font>
     <font>
@@ -40,14 +39,12 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -56,17 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00365F91"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE5CD"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,30 +88,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -489,33 +473,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hardware Analysis — FPGA (Xilinx Vivado, xc7a12ticsg325-1L, Artix-7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+          <t>FPGA results</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: RESULTS.md §2–§5, this repository. Out-of-context synthesis, single-threaded, period-searched (up to 7 iterations for the 3 Ascon-family designs, 3 for the 9 finalists). All 12 designs routed with zero errors.</t>
+          <t>Source: graphs/results.csv, produced by flow/run_vivado.sh -- Vivado 2026.1, xc7a12ticsg325-1L, out-of-context, single-threaded, identical 7-iteration period search for all 11 designs. Power is vectorless for every design.</t>
         </is>
       </c>
     </row>
@@ -527,12 +510,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Area — Slice LUTs</t>
+          <t>Area - Slice LUTs</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Area — Slice Registers</t>
+          <t>Area - Slice Registers</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -568,11 +551,6 @@
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Energy / bit (pJ)</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence / notes</t>
         </is>
       </c>
     </row>
@@ -583,154 +561,145 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="C5" s="5" t="n">
         <v>728</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>18.182</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>55</v>
+        <v>4.142</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>241.43</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>SAIF, RTL-sim activity (dynamic only, static 57 mW excluded)</t>
+          <t>vectorless (default activity estimate)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>880.0</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0.7993</v>
+          <t>3862.9</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>3.4429</t>
+        </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>20.5</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>KAT (1089/1089) + shared-FSM schedule (identical across all 3 Ascon-family)</t>
+          <t>34.2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>hybrid r=128</t>
+          <t>hybrid r=64</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>1021</v>
+        <v>874</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>663</v>
+        <v>600</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>18.4</v>
+        <v>7.171</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>54.35</v>
+        <v>139.45</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>SAIF, RTL-sim activity (dynamic only, static 57 mW excluded)</t>
+          <t>vectorless (default activity estimate)</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>870.0</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0.8521</v>
+          <t>1487.5</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>1.7019</t>
+        </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>shared-FSM schedule (identical across all 3 Ascon-family); not KAT-tested (no official suite)</t>
+          <t>55.8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>hybrid r=64</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>873</v>
+          <t>tinyjambu</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>473</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>599</v>
+        <v>533</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8.545</v>
+        <v>4.322</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>117.03</v>
+        <v>231.37</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>SAIF, RTL-sim activity (dynamic only, static 57 mW excluded)</t>
+          <t>vectorless (default activity estimate)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>936.0</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>1.0722</v>
+          <t>205.3</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>0.4340</t>
+        </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>20.3</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>shared-FSM schedule (identical across all 3 Ascon-family); not KAT-tested (no official suite)</t>
+          <t>389.7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>tinyjambu</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>472</v>
+          <t>xoodyak</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>1554</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>533</v>
+        <v>885</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>214.13</v>
+        <v>7.698</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>129.9</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -739,43 +708,40 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>190.0</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0.4025</v>
+          <t>1385.6</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>0.8917</t>
+        </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>399.0</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count confirmed identically 8/8 times</t>
+          <t>70.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>xoodyak</t>
+          <t>giftcofb</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1555</v>
+        <v>1530</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>885</v>
+        <v>1005</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>7.505</v>
+        <v>8.334</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>133.24</v>
+        <v>119.99</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -784,43 +750,40 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>1420.0</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0.9132</v>
+          <t>269.2</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>0.1759</t>
+        </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>68.3</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 1 clean block boundary only (not independently repeated)</t>
+          <t>252.6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>giftcofb</t>
+          <t>grain128aead</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>1531</v>
+        <v>598</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1005</v>
+        <v>915</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>7.912</v>
+        <v>4.667</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>126.39</v>
+        <v>214.27</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
@@ -829,43 +792,40 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>284.0</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0.1855</v>
+          <t>99.7</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>0.1668</t>
+        </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>240.0</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count confirmed identically 2/2 times</t>
+          <t>852.2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>grain</t>
+          <t>sparkle</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>587</v>
+        <v>2369</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>915</v>
+        <v>1093</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>5.795</v>
+        <v>13.437</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>172.56</v>
+        <v>74.42</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -874,43 +834,40 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>0.1363</v>
+          <t>545.1</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>0.2301</t>
+        </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>975.0</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 32-point linear fit (bit-serial, no block boundary)</t>
+          <t>192.6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>sparkle</t>
+          <t>elephant</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>2352</v>
+        <v>4625</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1093</v>
+        <v>2472</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>15.123</v>
+        <v>19.948</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>98</v>
+        <v>50.13</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>66</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -919,88 +876,82 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>484.0</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0.2058</v>
+          <t>47.6-95.2</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>0.0103-0.0206</t>
+        </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>203.0</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 1 clean block boundary (grid's max PT is exactly one rate block)</t>
+          <t>692.9-1385.9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>elephant</t>
+          <t>isap</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>4621</v>
+        <v>2358</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>2472</v>
+        <v>1651</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>22.217</v>
+        <v>6.093</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>45.01</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>64</v>
+        <v>164.12</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>134</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>vectorless (default activity estimate)</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>42.6–85.7</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>0.0139</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>750.0–1500.0</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count IRREGULAR - block crossing not a repeatable constant, reported as a bracket</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>262.4</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>0.1113</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>510.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>isap</t>
+          <t>photonbeetle</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>2347</v>
+        <v>2033</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1651</v>
+        <v>1090</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6.867</v>
+        <v>8.131</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>145.62</v>
+        <v>122.99</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -1009,43 +960,40 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>233.0</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>0.0993</v>
+          <t>642.9</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>0.3162</t>
+        </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>494.0</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count confirmed identically 4/4 times</t>
+          <t>121.3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>photonbeetle</t>
+          <t>romulus</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>2031</v>
+        <v>1498</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1090</v>
+        <v>1430</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>8.792</v>
+        <v>5.676</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>113.74</v>
+        <v>176.18</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1054,80 +1002,31 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>594.0</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>0.2925</v>
+          <t>490.3</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>0.3273</t>
+        </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 2 measurements, off by 1 cycle (24 then 25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>romulus</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>1385</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>1430</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>7.213</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>138.64</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>vectorless (default activity estimate)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>386.0</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.2787</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 1 clean block boundary only (not independently repeated)</t>
+          <t>159.1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Green = best (smallest area / highest Fmax / lowest power) in this column. Orange = bracket, not a single confirmed number (see elephant note).</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Green = best in column. Ranges (elephant) are excluded from the comparison, since they are brackets rather than point estimates.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1139,33 +1038,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hardware Analysis — ASIC (OpenROAD, SkyWater sky130hd, 130 nm, tt_025C_1v80)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="40" customHeight="1">
+          <t>ASIC results</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: RESULTS.md §2, §4, §5, this repository. yosys synthesis + OpenROAD place-and-route. The 3 Ascon-family designs got a full period sweep to their closing limit; the 9 finalists got one fixed, generous period each (sky130 Fmax there is a lower bound, not a searched maximum — RESULTS.md §1.2/§8.3).</t>
+          <t>Source: graphs/results.csv, produced by flow/run_sky130.sh -- yosys 0.38 + OpenROAD 2.0 on sky130hd (tt_025C_1v80), identical period search for all 11 designs, stopped after global routing. Power is vectorless for every design.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1075,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Area (µm²)</t>
+          <t>Area (um^2)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1212,17 +1110,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Throughput / Area (Gbit/s per mm²)</t>
+          <t>Throughput / Area (Gbit/s per mm^2)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Energy / bit (pJ)</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Confidence / notes</t>
         </is>
       </c>
     </row>
@@ -1233,154 +1126,145 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46605</v>
+        <v>62955</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>12416</v>
+        <v>16772</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3.9</v>
+        <v>3.837</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>256</v>
+        <v>260.6</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>88.7</v>
+        <v>88</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>VCD-annotated, RTL-sim activity (total power)</t>
+          <t>vectorless (default activity estimate)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>4100.0</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>87.973</v>
+          <t>4169.6</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>66.231</t>
+        </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>21.6</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>KAT (1089/1089) + shared-FSM schedule (identical across all 3 Ascon-family)</t>
+          <t>21.1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>hybrid r=128</t>
+          <t>hybrid r=64</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>41044</v>
+        <v>48304</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10935</v>
+        <v>12869</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>15.97</v>
+        <v>17.007</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>62.5</v>
+        <v>58.8</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>VCD-annotated, RTL-sim activity (total power)</t>
+          <t>vectorless (default activity estimate)</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1000.0</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>24.364</v>
+          <t>627.2</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>12.984</t>
+        </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>shared-FSM schedule (identical across all 3 Ascon-family); not KAT-tested (no official suite)</t>
+          <t>32.4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>hybrid r=64</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>36895</v>
+          <t>tinyjambu</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>27081</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9829</v>
+        <v>7215</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>23.7</v>
+        <v>3.327</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>10.1</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>VCD-annotated, RTL-sim activity (total power)</t>
+          <t>vectorless (default activity estimate)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>13.552</v>
+          <t>266.7</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>9.849</t>
+        </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>shared-FSM schedule (identical across all 3 Ascon-family); not KAT-tested (no official suite)</t>
+          <t>37.9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>tinyjambu</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>26514</v>
+          <t>xoodyak</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>74590</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>7064</v>
+        <v>19872</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>257</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>3.07</v>
+        <v>5.102</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>19.5</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
@@ -1389,43 +1273,40 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>228.0</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>8.599</v>
+          <t>2090.7</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>28.030</t>
+        </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>13.4</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count confirmed identically 8/8 times</t>
+          <t>9.3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>xoodyak</t>
+          <t>giftcofb</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>68960</v>
+        <v>61004</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>18372</v>
+        <v>16252</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>4.45</v>
+        <v>4.272</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>225</v>
+        <v>234.1</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>4.48</v>
+        <v>38.8</v>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
@@ -1434,43 +1315,40 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>2400.0</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>34.803</v>
+          <t>525.1</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>8.608</t>
+        </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 1 clean block boundary only (not independently repeated)</t>
+          <t>73.9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>giftcofb</t>
+          <t>grain128aead</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>59856</v>
+        <v>41247</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>15946</v>
+        <v>10989</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5.41</v>
+        <v>3.606</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>185</v>
+        <v>277.3</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>5.32</v>
+        <v>16.4</v>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
@@ -1479,43 +1357,40 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>415.0</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>6.933</v>
+          <t>129.1</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>3.130</t>
+        </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>12.8</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count confirmed identically 2/2 times</t>
+          <t>127.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>grain</t>
+          <t>sparkle</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>39196</v>
+        <v>140097</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>10442</v>
+        <v>37323</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>4.31</v>
+        <v>24.272</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>232</v>
+        <v>41.2</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>4.51</v>
+        <v>109</v>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
@@ -1524,43 +1399,40 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>2.755</v>
+          <t>301.8</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>2.154</t>
+        </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>41.9</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 32-point linear fit (bit-serial, no block boundary)</t>
+          <t>361.2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>sparkle</t>
+          <t>elephant</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>132133</v>
+        <v>173446</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>35202</v>
+        <v>46208</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>24.73</v>
+        <v>12.788</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>40</v>
+        <v>78.2</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>272.21</v>
+        <v>38.2</v>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
@@ -1569,88 +1441,82 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>293.0</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>2.217</v>
+          <t>74.3-148.6</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>0.428-0.857</t>
+        </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>930.0</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 1 clean block boundary (grid's max PT is exactly one rate block)</t>
+          <t>257.1-514.2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>elephant</t>
+          <t>isap</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>169458</v>
+        <v>106288</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>45145</v>
+        <v>28316</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>16.73</v>
+        <v>5.379</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>60</v>
+        <v>185.9</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>12.21</v>
+        <v>83.2</v>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
           <t>vectorless (default activity estimate)</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>57.0–114.0</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="J13" s="7" t="inlineStr">
-        <is>
-          <t>107.0–215.0</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count IRREGULAR - block crossing not a repeatable constant, reported as a bracket</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>297.3</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>2.797</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>279.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>isap</t>
+          <t>photonbeetle</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>104757</v>
+        <v>99503</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>27908</v>
+        <v>26509</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>5.07</v>
+        <v>8.961</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>197</v>
+        <v>111.6</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>27.21</v>
+        <v>56.8</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
@@ -1659,43 +1525,40 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>315.0</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>3.007</v>
+          <t>583.3</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>5.862</t>
+        </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>86.3</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count confirmed identically 4/4 times</t>
+          <t>97.4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>photonbeetle</t>
+          <t>romulus</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>98765</v>
+        <v>84876</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>26312</v>
+        <v>22612</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>8.369999999999999</v>
+        <v>4.876</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>119</v>
+        <v>205.1</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>16.88</v>
+        <v>38.7</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1704,80 +1567,31 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>622.0</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>6.298</v>
+          <t>570.8</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>6.725</t>
+        </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>27.2</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 2 measurements, off by 1 cycle (24 then 25)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>romulus</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>85117</v>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>22676</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>vectorless (default activity estimate)</t>
-        </is>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>551.0</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>6.473</v>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>12.7</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>KAT-verified; cycle count from 1 clean block boundary only (not independently repeated)</t>
+          <t>67.8</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Green = best (smallest area / highest Fmax / lowest power) in this column. Orange = bracket, not a single confirmed number (see elephant note). sparkle's power is flagged in RESULTS.md §4.2 as a likely vectorless-model artifact (98% combinational, single huge unregistered round) — treat its energy/bit with that caveat.</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Green = best in column. Ranges (elephant) are excluded from the comparison, since they are brackets rather than point estimates.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A17:K17"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1789,10 +1603,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1803,154 +1617,163 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>All 12 designs in verilog/: Ascon-AEAD128 (NIST SP 800-232), two experimental Ascon-SipHash hybrids (r=128, r=64), and the 9 NIST LWC finalists that lost to Ascon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="70" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>KAT verification</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>10 of 12 designs are now KAT-verified: Ascon-AEAD128 against the official 1089-vector NIST-format suite, and all 9 finalists against the official NIST LWC KAT grid (17127 or 19305 words each), after fixing 42 real RTL bugs across 8 finalist cores. The two hybrids have no official KAT suite to run against (not a NIST submission) — verified only via a 16×16 synthetic length grid against their C reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="98" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>All 11 designs in verilog/: Ascon-AEAD128 (NIST SP 800-232), one experimental Ascon-SipHash hybrid (r=64), and the 9 NIST LWC finalists that lost to Ascon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>One flow, all eleven</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Every figure on both sheets comes from a single measurement procedure applied identically to all 11 designs: the same period search, the same tool versions, the same power method. The previous edition of this workbook mixed two passes -- a deeper one for the 2 Ascon-family designs and a lighter survey for the 9 finalists -- which made several columns not directly comparable across rows. That asymmetry is gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Numbers differ from the previous edition</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>These are a fresh measurement, not a correction of individual figures. The original flow scripts were lost, so the flow was rebuilt (flow/ in this repository) and all 11 designs re-measured on Vivado 2026.1 and OpenROAD 2.0. Register counts reproduce exactly on all 11 designs and sky130 area reproduces within a few percent on the 9 finalists, which is the evidence that the rebuild is sound. See RESULTS.md for what changed and why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Power is vectorless everywhere</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Both sheets' power is a vectorless default-activity estimate for all 11 designs. The previous edition had simulation-derived activity (SAIF on FPGA, VCD on sky130) for the 2 Ascon-family designs; that stimulus was not kept and could not be reproduced. This makes the column uniform across rows, but it is a real accuracy downgrade for those two designs. Read vectorless power as relative ordering, not absolute silicon power.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Energy / bit</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>power / throughput, using total power, consistently for all 11 designs. The previous edition divided by dynamic-only power for the 2 Ascon-family FPGA rows and total power for the other 9, so its FPGA energy/bit column was not comparable across rows. This one is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Throughput methodology</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Ascon-family (3 designs): documented, simulation-confirmed FSM schedule (8 cycles/block). Finalists (9 designs): extracted 2026-09-03 by replaying each design's own already-passing KAT stimulus through a cycle-instrumented testbench and differencing transaction timestamps across message lengths to isolate the marginal per-block cost. Confidence varies per design — see the 'Confidence / notes' column on each sheet; several (xoodyak, sparkle, romulus) rest on a single clean block-boundary measurement, not independently repeated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="84" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Elephant — bracket, not a point estimate</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>elephant's block-boundary crossing is not a clean, repeatable constant: the first Spongent-π[160] call costs 84 cycles, but crossing the second block costs two such calls back-to-back (169 cycles), not one. Both bounds are real, simulation-observed numbers; which best represents a long message is unresolved by the available KAT vector range (0–32 bytes). Its throughput, throughput/area and energy/bit cells are reported as ranges (shaded orange) rather than a single invented number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>FPGA energy/bit is NOT apples-to-apples across all 12</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>The 3 Ascon-family FPGA energy/bit figures divide by DYNAMIC power only (SAIF-annotated; the 57 mW static/clock floor, a fixed device property, is excluded). The 9 finalists' vectorless FPGA power was never split into dynamic/static, so their FPGA energy/bit divides by TOTAL power — making their FPGA pJ/bit numbers look worse by construction, not necessarily by design. sky130 (ASIC) energy/bit uses total power for all 12 alike, so that column IS directly comparable across every design.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="70" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Power measurement depth differs by design tier</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>The 3 Ascon-family designs got real, simulation-derived activity (SAIF for FPGA, VCD for sky130) in addition to a vectorless estimate. The 9 finalists got vectorless (default-activity-estimate) power only, on both targets. Vectorless numbers should be read as relative ordering, not absolute silicon power — sparkle's sky130 figure (272 mW, 98% combinational) is flagged in RESULTS.md as a likely artifact of this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>sky130 Fmax for the 9 finalists is a lower bound</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Only tried at one generous starting period each (vs. a full sweep-to-limit for the 3 Ascon-family designs) — real ceiling is likely higher for most of them. See RESULTS.md §1.2, §4.1, §8.3.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="70" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>throughput = Max Frequency x bits-per-cycle, where bits-per-cycle is each design's own RTL cycle schedule (RESULTS.md 5). That schedule is a property of the RTL and is unchanged by re-measurement; the same constants reproduce the previous edition's throughput figures to within rounding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Elephant - bracket, not a point estimate</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>elephant's block-boundary crossing is not a repeatable constant: the first Spongent-pi[160] call costs 84 cycles, but crossing the second block costs two back-to-back (169), not one. Both bounds are real, simulation-observed numbers, so its throughput, throughput/area and energy/bit are ranges and are excluded from the best-in-column highlighting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>sparkle floorplan</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>sparkle is the only design that would not route at the 45% target utilization used for the other ten; it was placed at 30% instead. Area here is summed instance area, which is unaffected by floorplan utilization, so the comparison holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Area definitions</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>FPGA area = Slice LUTs (the conventional single-number FPGA area metric; Slice Registers given alongside for completeness — occupied-slice figures were only recorded for the 3 Ascon-family designs' deeper pass, not the finalists). ASIC area = post-place-and-route cell area in µm²; GE = gate equivalents = cell area ÷ sky130 NAND2 area (3.7536 µm²).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="56" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>FPGA area = Slice LUTs, with Slice Registers alongside. ASIC area = summed placed-instance area in um^2 after global routing; GE = that area divided by the sky130hd NAND2_1 cell area of 3.7536 um^2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Critical path delay</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>FPGA: the best achieved period from a multi-iteration Vivado search (constraint − WNS). ASIC: sky130 period minus setup slack at the design's measured/searched period — both consistent with, and Max Frequency = 1 / Critical Path Delay for, the already-published Fmax figures in RESULTS.md §2's headline table.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="56" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>The best period each design closed at under an identical binary search, with zero unrouted nets (FPGA) and non-negative worst slack. Max Frequency = 1 / Critical Path Delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Not security claims</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Smaller / faster / lower-power is not "better" in isolation — these 12 designs have different key/tag sizes, round counts and security margins, and the two hybrids are unanalysed constructions with no cryptanalysis. See RESULTS.md §8 in full before treating any number here as a security or deployment recommendation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="70" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Smaller / faster / lower-power is not 'better' in isolation -- these 11 designs have different key/tag sizes, round counts and security margins, and the hybrid is an unanalysed construction with no cryptanalysis. See RESULTS.md 8 before treating any number here as a security or deployment recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>Every number on the FPGA and ASIC sheets is transcribed from RESULTS.md in this repository (§2–§5), which in turn cites the exact Vivado/OpenROAD/yosys log for each figure in its §10 provenance table. This workbook adds only two derived columns per sheet (Throughput/Area, and the unit conversions needed to compute it) — it introduces no new measurements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>graphs/results.csv in this repository, written by flow/merge_results.py from the two sweep CSVs. This workbook adds only derived columns (throughput, throughput/area, energy/bit) and hardcodes no measured value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Generated</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-03, from this repository's RESULTS.md.</t>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-07, by flow/build_hw_xlsx.py.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>